--- a/Excel Files/Book1.xlsx
+++ b/Excel Files/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tonye\OneDrive\Desktop\JavaApps\Excel Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5AF0127-8B44-4418-B068-B128B261E22A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{826659FA-43B0-4623-A39F-FB71E69ED84F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" firstSheet="1" activeTab="3" xr2:uid="{B3B917DC-F552-4F28-9100-674774D75A2B}"/>
+    <workbookView minimized="1" xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9420" firstSheet="1" activeTab="3" xr2:uid="{B3B917DC-F552-4F28-9100-674774D75A2B}"/>
   </bookViews>
   <sheets>
     <sheet name="Relative cell reference" sheetId="4" r:id="rId1"/>
@@ -1281,55 +1281,55 @@
       </c>
       <c r="D5" s="5">
         <f ca="1">SUM('North Branch:West Branch'!B3)</f>
-        <v>30684</v>
+        <v>29689</v>
       </c>
       <c r="E5" s="5">
         <f ca="1">SUM('North Branch:West Branch'!C3)</f>
-        <v>26334</v>
+        <v>24343</v>
       </c>
       <c r="F5" s="5">
         <f ca="1">SUM('North Branch:West Branch'!D3)</f>
-        <v>34571</v>
+        <v>32866</v>
       </c>
       <c r="G5" s="5">
         <f ca="1">SUM('North Branch:West Branch'!E3)</f>
-        <v>25643</v>
+        <v>28304</v>
       </c>
       <c r="H5" s="5">
         <f ca="1">SUM('North Branch:West Branch'!F3)</f>
-        <v>27528</v>
+        <v>27850</v>
       </c>
       <c r="I5" s="5">
         <f ca="1">SUM('North Branch:West Branch'!G3)</f>
-        <v>32841</v>
+        <v>33027</v>
       </c>
       <c r="J5" s="5">
         <f ca="1">SUM('North Branch:West Branch'!H3)</f>
-        <v>31261</v>
+        <v>30510</v>
       </c>
       <c r="K5" s="5">
         <f ca="1">SUM('North Branch:West Branch'!I3)</f>
-        <v>30614</v>
+        <v>26523</v>
       </c>
       <c r="L5" s="5">
         <f ca="1">SUM('North Branch:West Branch'!J3)</f>
-        <v>30049</v>
+        <v>30548</v>
       </c>
       <c r="M5" s="5">
         <f ca="1">SUM('North Branch:West Branch'!K3)</f>
-        <v>31385</v>
+        <v>32035</v>
       </c>
       <c r="N5" s="5">
         <f ca="1">SUM('North Branch:West Branch'!L3)</f>
-        <v>32000</v>
+        <v>27829</v>
       </c>
       <c r="O5" s="5">
         <f ca="1">SUM('North Branch:West Branch'!M3)</f>
-        <v>28917</v>
+        <v>29242</v>
       </c>
       <c r="P5" s="5">
         <f ca="1">SUM(D5:O5)</f>
-        <v>361827</v>
+        <v>352766</v>
       </c>
     </row>
     <row r="6" spans="3:16" x14ac:dyDescent="0.3">
@@ -1338,55 +1338,55 @@
       </c>
       <c r="D6" s="5">
         <f ca="1">SUM('North Branch:West Branch'!B4)</f>
-        <v>30198</v>
+        <v>28180</v>
       </c>
       <c r="E6" s="5">
         <f ca="1">SUM('North Branch:West Branch'!C4)</f>
-        <v>29661</v>
+        <v>27803</v>
       </c>
       <c r="F6" s="5">
         <f ca="1">SUM('North Branch:West Branch'!D4)</f>
-        <v>30200</v>
+        <v>31661</v>
       </c>
       <c r="G6" s="5">
         <f ca="1">SUM('North Branch:West Branch'!E4)</f>
-        <v>29272</v>
+        <v>29758</v>
       </c>
       <c r="H6" s="5">
         <f ca="1">SUM('North Branch:West Branch'!F4)</f>
-        <v>34371</v>
+        <v>29692</v>
       </c>
       <c r="I6" s="5">
         <f ca="1">SUM('North Branch:West Branch'!G4)</f>
-        <v>30604</v>
+        <v>30521</v>
       </c>
       <c r="J6" s="5">
         <f ca="1">SUM('North Branch:West Branch'!H4)</f>
-        <v>31780</v>
+        <v>34255</v>
       </c>
       <c r="K6" s="5">
         <f ca="1">SUM('North Branch:West Branch'!I4)</f>
-        <v>33523</v>
+        <v>35306</v>
       </c>
       <c r="L6" s="5">
         <f ca="1">SUM('North Branch:West Branch'!J4)</f>
-        <v>33372</v>
+        <v>33094</v>
       </c>
       <c r="M6" s="5">
         <f ca="1">SUM('North Branch:West Branch'!K4)</f>
-        <v>30251</v>
+        <v>31184</v>
       </c>
       <c r="N6" s="5">
         <f ca="1">SUM('North Branch:West Branch'!L4)</f>
-        <v>29380</v>
+        <v>26689</v>
       </c>
       <c r="O6" s="5">
         <f ca="1">SUM('North Branch:West Branch'!M4)</f>
-        <v>31649</v>
+        <v>31468</v>
       </c>
       <c r="P6" s="5">
         <f t="shared" ref="P6:P12" ca="1" si="0">SUM(D6:O6)</f>
-        <v>374261</v>
+        <v>369611</v>
       </c>
     </row>
     <row r="7" spans="3:16" x14ac:dyDescent="0.3">
@@ -1395,55 +1395,55 @@
       </c>
       <c r="D7" s="5">
         <f ca="1">SUM('North Branch:West Branch'!B5)</f>
-        <v>30525</v>
+        <v>29199</v>
       </c>
       <c r="E7" s="5">
         <f ca="1">SUM('North Branch:West Branch'!C5)</f>
-        <v>30830</v>
+        <v>33668</v>
       </c>
       <c r="F7" s="5">
         <f ca="1">SUM('North Branch:West Branch'!D5)</f>
-        <v>25399</v>
+        <v>25875</v>
       </c>
       <c r="G7" s="5">
         <f ca="1">SUM('North Branch:West Branch'!E5)</f>
-        <v>35637</v>
+        <v>33873</v>
       </c>
       <c r="H7" s="5">
         <f ca="1">SUM('North Branch:West Branch'!F5)</f>
-        <v>24489</v>
+        <v>24384</v>
       </c>
       <c r="I7" s="5">
         <f ca="1">SUM('North Branch:West Branch'!G5)</f>
-        <v>30782</v>
+        <v>29164</v>
       </c>
       <c r="J7" s="5">
         <f ca="1">SUM('North Branch:West Branch'!H5)</f>
-        <v>25610</v>
+        <v>25544</v>
       </c>
       <c r="K7" s="5">
         <f ca="1">SUM('North Branch:West Branch'!I5)</f>
-        <v>28348</v>
+        <v>28739</v>
       </c>
       <c r="L7" s="5">
         <f ca="1">SUM('North Branch:West Branch'!J5)</f>
-        <v>28633</v>
+        <v>26050</v>
       </c>
       <c r="M7" s="5">
         <f ca="1">SUM('North Branch:West Branch'!K5)</f>
-        <v>30905</v>
+        <v>31955</v>
       </c>
       <c r="N7" s="5">
         <f ca="1">SUM('North Branch:West Branch'!L5)</f>
-        <v>34913</v>
+        <v>31512</v>
       </c>
       <c r="O7" s="5">
         <f ca="1">SUM('North Branch:West Branch'!M5)</f>
-        <v>35108</v>
+        <v>36545</v>
       </c>
       <c r="P7" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>361179</v>
+        <v>356508</v>
       </c>
     </row>
     <row r="8" spans="3:16" x14ac:dyDescent="0.3">
@@ -1452,55 +1452,55 @@
       </c>
       <c r="D8" s="5">
         <f ca="1">SUM('North Branch:West Branch'!B6)</f>
-        <v>27877</v>
+        <v>27012</v>
       </c>
       <c r="E8" s="5">
         <f ca="1">SUM('North Branch:West Branch'!C6)</f>
-        <v>33272</v>
+        <v>31305</v>
       </c>
       <c r="F8" s="5">
         <f ca="1">SUM('North Branch:West Branch'!D6)</f>
-        <v>25864</v>
+        <v>28364</v>
       </c>
       <c r="G8" s="5">
         <f ca="1">SUM('North Branch:West Branch'!E6)</f>
-        <v>32958</v>
+        <v>31042</v>
       </c>
       <c r="H8" s="5">
         <f ca="1">SUM('North Branch:West Branch'!F6)</f>
-        <v>27390</v>
+        <v>27310</v>
       </c>
       <c r="I8" s="5">
         <f ca="1">SUM('North Branch:West Branch'!G6)</f>
-        <v>35046</v>
+        <v>33714</v>
       </c>
       <c r="J8" s="5">
         <f ca="1">SUM('North Branch:West Branch'!H6)</f>
-        <v>30803</v>
+        <v>30451</v>
       </c>
       <c r="K8" s="5">
         <f ca="1">SUM('North Branch:West Branch'!I6)</f>
-        <v>27586</v>
+        <v>28683</v>
       </c>
       <c r="L8" s="5">
         <f ca="1">SUM('North Branch:West Branch'!J6)</f>
-        <v>32132</v>
+        <v>33656</v>
       </c>
       <c r="M8" s="5">
         <f ca="1">SUM('North Branch:West Branch'!K6)</f>
-        <v>33219</v>
+        <v>32920</v>
       </c>
       <c r="N8" s="5">
         <f ca="1">SUM('North Branch:West Branch'!L6)</f>
-        <v>32063</v>
+        <v>31450</v>
       </c>
       <c r="O8" s="5">
         <f ca="1">SUM('North Branch:West Branch'!M6)</f>
-        <v>32998</v>
+        <v>31767</v>
       </c>
       <c r="P8" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>371208</v>
+        <v>367674</v>
       </c>
     </row>
     <row r="9" spans="3:16" x14ac:dyDescent="0.3">
@@ -1509,55 +1509,55 @@
       </c>
       <c r="D9" s="5">
         <f ca="1">SUM('North Branch:West Branch'!B7)</f>
-        <v>31404</v>
+        <v>31110</v>
       </c>
       <c r="E9" s="5">
         <f ca="1">SUM('North Branch:West Branch'!C7)</f>
-        <v>30705</v>
+        <v>28806</v>
       </c>
       <c r="F9" s="5">
         <f ca="1">SUM('North Branch:West Branch'!D7)</f>
-        <v>34228</v>
+        <v>36215</v>
       </c>
       <c r="G9" s="5">
         <f ca="1">SUM('North Branch:West Branch'!E7)</f>
-        <v>27454</v>
+        <v>25595</v>
       </c>
       <c r="H9" s="5">
         <f ca="1">SUM('North Branch:West Branch'!F7)</f>
-        <v>35860</v>
+        <v>34957</v>
       </c>
       <c r="I9" s="5">
         <f ca="1">SUM('North Branch:West Branch'!G7)</f>
-        <v>32057</v>
+        <v>34476</v>
       </c>
       <c r="J9" s="5">
         <f ca="1">SUM('North Branch:West Branch'!H7)</f>
-        <v>29863</v>
+        <v>32913</v>
       </c>
       <c r="K9" s="5">
         <f ca="1">SUM('North Branch:West Branch'!I7)</f>
-        <v>33261</v>
+        <v>31244</v>
       </c>
       <c r="L9" s="5">
         <f ca="1">SUM('North Branch:West Branch'!J7)</f>
-        <v>23612</v>
+        <v>25901</v>
       </c>
       <c r="M9" s="5">
         <f ca="1">SUM('North Branch:West Branch'!K7)</f>
-        <v>30030</v>
+        <v>34109</v>
       </c>
       <c r="N9" s="5">
         <f ca="1">SUM('North Branch:West Branch'!L7)</f>
-        <v>36562</v>
+        <v>37886</v>
       </c>
       <c r="O9" s="5">
         <f ca="1">SUM('North Branch:West Branch'!M7)</f>
-        <v>27451</v>
+        <v>29431</v>
       </c>
       <c r="P9" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>372487</v>
+        <v>382643</v>
       </c>
     </row>
     <row r="10" spans="3:16" x14ac:dyDescent="0.3">
@@ -1566,55 +1566,55 @@
       </c>
       <c r="D10" s="5">
         <f ca="1">SUM('North Branch:West Branch'!B8)</f>
-        <v>31088</v>
+        <v>30395</v>
       </c>
       <c r="E10" s="5">
         <f ca="1">SUM('North Branch:West Branch'!C8)</f>
-        <v>27051</v>
+        <v>28533</v>
       </c>
       <c r="F10" s="5">
         <f ca="1">SUM('North Branch:West Branch'!D8)</f>
-        <v>30098</v>
+        <v>27156</v>
       </c>
       <c r="G10" s="5">
         <f ca="1">SUM('North Branch:West Branch'!E8)</f>
-        <v>31653</v>
+        <v>29932</v>
       </c>
       <c r="H10" s="5">
         <f ca="1">SUM('North Branch:West Branch'!F8)</f>
-        <v>30363</v>
+        <v>33849</v>
       </c>
       <c r="I10" s="5">
         <f ca="1">SUM('North Branch:West Branch'!G8)</f>
-        <v>31178</v>
+        <v>27892</v>
       </c>
       <c r="J10" s="5">
         <f ca="1">SUM('North Branch:West Branch'!H8)</f>
-        <v>29868</v>
+        <v>29695</v>
       </c>
       <c r="K10" s="5">
         <f ca="1">SUM('North Branch:West Branch'!I8)</f>
-        <v>31902</v>
+        <v>33035</v>
       </c>
       <c r="L10" s="5">
         <f ca="1">SUM('North Branch:West Branch'!J8)</f>
-        <v>33146</v>
+        <v>30658</v>
       </c>
       <c r="M10" s="5">
         <f ca="1">SUM('North Branch:West Branch'!K8)</f>
-        <v>32045</v>
+        <v>33360</v>
       </c>
       <c r="N10" s="5">
         <f ca="1">SUM('North Branch:West Branch'!L8)</f>
-        <v>34639</v>
+        <v>34926</v>
       </c>
       <c r="O10" s="5">
         <f ca="1">SUM('North Branch:West Branch'!M8)</f>
-        <v>34530</v>
+        <v>34690</v>
       </c>
       <c r="P10" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>377561</v>
+        <v>374121</v>
       </c>
     </row>
     <row r="11" spans="3:16" x14ac:dyDescent="0.3">
@@ -1623,55 +1623,55 @@
       </c>
       <c r="D11" s="5">
         <f ca="1">SUM('North Branch:West Branch'!B9)</f>
-        <v>28393</v>
+        <v>27912</v>
       </c>
       <c r="E11" s="5">
         <f ca="1">SUM('North Branch:West Branch'!C9)</f>
-        <v>31677</v>
+        <v>29271</v>
       </c>
       <c r="F11" s="5">
         <f ca="1">SUM('North Branch:West Branch'!D9)</f>
-        <v>27305</v>
+        <v>26906</v>
       </c>
       <c r="G11" s="5">
         <f ca="1">SUM('North Branch:West Branch'!E9)</f>
-        <v>26821</v>
+        <v>27131</v>
       </c>
       <c r="H11" s="5">
         <f ca="1">SUM('North Branch:West Branch'!F9)</f>
-        <v>29011</v>
+        <v>28237</v>
       </c>
       <c r="I11" s="5">
         <f ca="1">SUM('North Branch:West Branch'!G9)</f>
-        <v>25607</v>
+        <v>24075</v>
       </c>
       <c r="J11" s="5">
         <f ca="1">SUM('North Branch:West Branch'!H9)</f>
-        <v>34094</v>
+        <v>35015</v>
       </c>
       <c r="K11" s="5">
         <f ca="1">SUM('North Branch:West Branch'!I9)</f>
-        <v>36565</v>
+        <v>32587</v>
       </c>
       <c r="L11" s="5">
         <f ca="1">SUM('North Branch:West Branch'!J9)</f>
-        <v>29206</v>
+        <v>33446</v>
       </c>
       <c r="M11" s="5">
         <f ca="1">SUM('North Branch:West Branch'!K9)</f>
-        <v>29155</v>
+        <v>26453</v>
       </c>
       <c r="N11" s="5">
         <f ca="1">SUM('North Branch:West Branch'!L9)</f>
-        <v>30552</v>
+        <v>31038</v>
       </c>
       <c r="O11" s="5">
         <f ca="1">SUM('North Branch:West Branch'!M9)</f>
-        <v>28071</v>
+        <v>28799</v>
       </c>
       <c r="P11" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>356457</v>
+        <v>350870</v>
       </c>
     </row>
     <row r="12" spans="3:16" x14ac:dyDescent="0.3">
@@ -1680,55 +1680,55 @@
       </c>
       <c r="D12" s="5">
         <f ca="1">SUM('North Branch:West Branch'!B10)</f>
-        <v>28303</v>
+        <v>30360</v>
       </c>
       <c r="E12" s="5">
         <f ca="1">SUM('North Branch:West Branch'!C10)</f>
-        <v>36296</v>
+        <v>32101</v>
       </c>
       <c r="F12" s="5">
         <f ca="1">SUM('North Branch:West Branch'!D10)</f>
-        <v>35034</v>
+        <v>33909</v>
       </c>
       <c r="G12" s="5">
         <f ca="1">SUM('North Branch:West Branch'!E10)</f>
-        <v>29997</v>
+        <v>31917</v>
       </c>
       <c r="H12" s="5">
         <f ca="1">SUM('North Branch:West Branch'!F10)</f>
-        <v>29476</v>
+        <v>33217</v>
       </c>
       <c r="I12" s="5">
         <f ca="1">SUM('North Branch:West Branch'!G10)</f>
-        <v>31241</v>
+        <v>35909</v>
       </c>
       <c r="J12" s="5">
         <f ca="1">SUM('North Branch:West Branch'!H10)</f>
-        <v>27026</v>
+        <v>27885</v>
       </c>
       <c r="K12" s="5">
         <f ca="1">SUM('North Branch:West Branch'!I10)</f>
-        <v>31542</v>
+        <v>31695</v>
       </c>
       <c r="L12" s="5">
         <f ca="1">SUM('North Branch:West Branch'!J10)</f>
-        <v>32747</v>
+        <v>31619</v>
       </c>
       <c r="M12" s="5">
         <f ca="1">SUM('North Branch:West Branch'!K10)</f>
-        <v>28667</v>
+        <v>29268</v>
       </c>
       <c r="N12" s="5">
         <f ca="1">SUM('North Branch:West Branch'!L10)</f>
-        <v>29151</v>
+        <v>25667</v>
       </c>
       <c r="O12" s="5">
         <f ca="1">SUM('North Branch:West Branch'!M10)</f>
-        <v>28206</v>
+        <v>27915</v>
       </c>
       <c r="P12" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>367686</v>
+        <v>371462</v>
       </c>
     </row>
     <row r="14" spans="3:16" x14ac:dyDescent="0.3">
@@ -1749,7 +1749,7 @@
       <c r="O14" s="3"/>
       <c r="P14" s="9">
         <f ca="1">SUM(P5:P12)</f>
-        <v>2942666</v>
+        <v>2925655</v>
       </c>
     </row>
   </sheetData>
@@ -3237,55 +3237,55 @@
       </c>
       <c r="B3" s="5">
         <f ca="1">SUM(RANDBETWEEN(5000,10000))</f>
-        <v>7272</v>
+        <v>6277</v>
       </c>
       <c r="C3" s="5">
         <f t="shared" ref="C3:M3" ca="1" si="0">SUM(RANDBETWEEN(5000,10000))</f>
-        <v>7079</v>
+        <v>5088</v>
       </c>
       <c r="D3" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>9318</v>
+        <v>7613</v>
       </c>
       <c r="E3" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>5469</v>
+        <v>8130</v>
       </c>
       <c r="F3" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>8031</v>
+        <v>8353</v>
       </c>
       <c r="G3" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>9106</v>
+        <v>9292</v>
       </c>
       <c r="H3" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>9072</v>
+        <v>8321</v>
       </c>
       <c r="I3" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>9284</v>
+        <v>5193</v>
       </c>
       <c r="J3" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>9392</v>
+        <v>9891</v>
       </c>
       <c r="K3" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>7706</v>
+        <v>8356</v>
       </c>
       <c r="L3" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>9637</v>
+        <v>5466</v>
       </c>
       <c r="M3" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>7991</v>
+        <v>8316</v>
       </c>
       <c r="N3" s="5">
         <f ca="1">SUM(B3:M3)</f>
-        <v>99357</v>
+        <v>90296</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -3294,55 +3294,55 @@
       </c>
       <c r="B4" s="5">
         <f t="shared" ref="B4:M10" ca="1" si="1">SUM(RANDBETWEEN(5000,10000))</f>
-        <v>7443</v>
+        <v>5425</v>
       </c>
       <c r="C4" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>7900</v>
+        <v>6042</v>
       </c>
       <c r="D4" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>8257</v>
+        <v>9718</v>
       </c>
       <c r="E4" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>8831</v>
+        <v>9317</v>
       </c>
       <c r="F4" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>9929</v>
+        <v>5250</v>
       </c>
       <c r="G4" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>5631</v>
+        <v>5548</v>
       </c>
       <c r="H4" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>5433</v>
+        <v>7908</v>
       </c>
       <c r="I4" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>7834</v>
+        <v>9617</v>
       </c>
       <c r="J4" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>9267</v>
+        <v>8989</v>
       </c>
       <c r="K4" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>6585</v>
+        <v>7518</v>
       </c>
       <c r="L4" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>7795</v>
+        <v>5104</v>
       </c>
       <c r="M4" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>7755</v>
+        <v>7574</v>
       </c>
       <c r="N4" s="5">
         <f t="shared" ref="N4:N10" ca="1" si="2">SUM(B4:M4)</f>
-        <v>92660</v>
+        <v>88010</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -3351,55 +3351,55 @@
       </c>
       <c r="B5" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>8884</v>
+        <v>7558</v>
       </c>
       <c r="C5" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>6690</v>
+        <v>9528</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>8074</v>
+        <v>8550</v>
       </c>
       <c r="E5" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>9026</v>
+        <v>7262</v>
       </c>
       <c r="F5" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>5709</v>
+        <v>5604</v>
       </c>
       <c r="G5" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>7823</v>
+        <v>6205</v>
       </c>
       <c r="H5" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>5291</v>
+        <v>5225</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>6277</v>
+        <v>6668</v>
       </c>
       <c r="J5" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>7676</v>
+        <v>5093</v>
       </c>
       <c r="K5" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>8556</v>
+        <v>9606</v>
       </c>
       <c r="L5" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>9598</v>
+        <v>6197</v>
       </c>
       <c r="M5" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>6639</v>
+        <v>8076</v>
       </c>
       <c r="N5" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>90243</v>
+        <v>85572</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -3408,55 +3408,55 @@
       </c>
       <c r="B6" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>7317</v>
+        <v>6452</v>
       </c>
       <c r="C6" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>8648</v>
+        <v>6681</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>7429</v>
+        <v>9929</v>
       </c>
       <c r="E6" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>7602</v>
+        <v>5686</v>
       </c>
       <c r="F6" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>6471</v>
+        <v>6391</v>
       </c>
       <c r="G6" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>7161</v>
+        <v>5829</v>
       </c>
       <c r="H6" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>8611</v>
+        <v>8259</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>7627</v>
+        <v>8724</v>
       </c>
       <c r="J6" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>7291</v>
+        <v>8815</v>
       </c>
       <c r="K6" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>9291</v>
+        <v>8992</v>
       </c>
       <c r="L6" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>8560</v>
+        <v>7947</v>
       </c>
       <c r="M6" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>9387</v>
+        <v>8156</v>
       </c>
       <c r="N6" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>95395</v>
+        <v>91861</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -3465,55 +3465,55 @@
       </c>
       <c r="B7" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>8935</v>
+        <v>8641</v>
       </c>
       <c r="C7" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>7113</v>
+        <v>5214</v>
       </c>
       <c r="D7" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>7690</v>
+        <v>9677</v>
       </c>
       <c r="E7" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>8329</v>
+        <v>6470</v>
       </c>
       <c r="F7" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>9678</v>
+        <v>8775</v>
       </c>
       <c r="G7" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>7010</v>
+        <v>9429</v>
       </c>
       <c r="H7" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>5936</v>
+        <v>8986</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>7247</v>
+        <v>5230</v>
       </c>
       <c r="J7" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>5010</v>
+        <v>7299</v>
       </c>
       <c r="K7" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>5057</v>
+        <v>9136</v>
       </c>
       <c r="L7" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>7999</v>
+        <v>9323</v>
       </c>
       <c r="M7" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>5767</v>
+        <v>7747</v>
       </c>
       <c r="N7" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>85771</v>
+        <v>95927</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -3522,55 +3522,55 @@
       </c>
       <c r="B8" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>8257</v>
+        <v>7564</v>
       </c>
       <c r="C8" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>5637</v>
+        <v>7119</v>
       </c>
       <c r="D8" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>8888</v>
+        <v>5946</v>
       </c>
       <c r="E8" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>8374</v>
+        <v>6653</v>
       </c>
       <c r="F8" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>6248</v>
+        <v>9734</v>
       </c>
       <c r="G8" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>9006</v>
+        <v>5720</v>
       </c>
       <c r="H8" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>9689</v>
+        <v>9516</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>7007</v>
+        <v>8140</v>
       </c>
       <c r="J8" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>8912</v>
+        <v>6424</v>
       </c>
       <c r="K8" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>7736</v>
+        <v>9051</v>
       </c>
       <c r="L8" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>9351</v>
+        <v>9638</v>
       </c>
       <c r="M8" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>9519</v>
+        <v>9679</v>
       </c>
       <c r="N8" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>98624</v>
+        <v>95184</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -3579,55 +3579,55 @@
       </c>
       <c r="B9" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>6673</v>
+        <v>6192</v>
       </c>
       <c r="C9" s="5">
         <f t="shared" ca="1" si="1"/>
+        <v>6313</v>
+      </c>
+      <c r="D9" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>7981</v>
+      </c>
+      <c r="E9" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>5696</v>
+      </c>
+      <c r="F9" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>8741</v>
+      </c>
+      <c r="G9" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>5220</v>
+      </c>
+      <c r="H9" s="5">
+        <f t="shared" ca="1" si="1"/>
         <v>8719</v>
       </c>
-      <c r="D9" s="5">
-        <f t="shared" ca="1" si="1"/>
-        <v>8380</v>
-      </c>
-      <c r="E9" s="5">
-        <f t="shared" ca="1" si="1"/>
-        <v>5386</v>
-      </c>
-      <c r="F9" s="5">
-        <f t="shared" ca="1" si="1"/>
-        <v>9515</v>
-      </c>
-      <c r="G9" s="5">
-        <f t="shared" ca="1" si="1"/>
-        <v>6752</v>
-      </c>
-      <c r="H9" s="5">
-        <f t="shared" ca="1" si="1"/>
-        <v>7798</v>
-      </c>
       <c r="I9" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>9742</v>
+        <v>5764</v>
       </c>
       <c r="J9" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>5250</v>
+        <v>9490</v>
       </c>
       <c r="K9" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>8469</v>
+        <v>5767</v>
       </c>
       <c r="L9" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>7704</v>
+        <v>8190</v>
       </c>
       <c r="M9" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>7718</v>
+        <v>8446</v>
       </c>
       <c r="N9" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>92106</v>
+        <v>86519</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -3636,55 +3636,55 @@
       </c>
       <c r="B10" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>5211</v>
+        <v>7268</v>
       </c>
       <c r="C10" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>9871</v>
+        <v>5676</v>
       </c>
       <c r="D10" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>6523</v>
+        <v>5398</v>
       </c>
       <c r="E10" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>5715</v>
+        <v>7635</v>
       </c>
       <c r="F10" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>5069</v>
+        <v>8810</v>
       </c>
       <c r="G10" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>5238</v>
+        <v>9906</v>
       </c>
       <c r="H10" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>6900</v>
+        <v>7759</v>
       </c>
       <c r="I10" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>8344</v>
+        <v>8497</v>
       </c>
       <c r="J10" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>8380</v>
+        <v>7252</v>
       </c>
       <c r="K10" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>9330</v>
+        <v>9931</v>
       </c>
       <c r="L10" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>8704</v>
+        <v>5220</v>
       </c>
       <c r="M10" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>9588</v>
+        <v>9297</v>
       </c>
       <c r="N10" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>88873</v>
+        <v>92649</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -3705,7 +3705,7 @@
       <c r="M12" s="3"/>
       <c r="N12" s="6">
         <f ca="1">SUM(N3:N10)</f>
-        <v>743029</v>
+        <v>726018</v>
       </c>
     </row>
   </sheetData>
